--- a/data/dataset_inventory.xlsx
+++ b/data/dataset_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abiga\Portfolio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2A3C5B-CF40-462A-8014-B610EBD5C734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD0ADE9-6D46-46B6-8A97-78BD6984E462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-5505" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="133">
   <si>
     <t>Dataset Name</t>
   </si>
@@ -44,9 +44,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Tags</t>
-  </si>
-  <si>
     <t>AARP Livable Communities Map</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
     <t>https://irma.nps.gov/DataStore/Reference/Profile/2237271</t>
   </si>
   <si>
-    <t>NPS, GIS, Data Standards</t>
-  </si>
-  <si>
     <t>Dept. of Commerce – National Travel and Tourism Office Research Portal</t>
   </si>
   <si>
@@ -158,232 +152,283 @@
     <t>Housing and transportation affordability</t>
   </si>
   <si>
+    <t>Large-Scale Solar Projects Map</t>
+  </si>
+  <si>
+    <t>https://www.usgs.gov/news/national-news-release/usgs-and-lawrence-berkeley-national-laboratory-release-database-and</t>
+  </si>
+  <si>
+    <t>NPS Mortality Data</t>
+  </si>
+  <si>
+    <t>https://www.nps.gov/orgs/1336/data.htm#:~:text=Key%20Mortality%20Statistics%3A%201%20A%20total%20of%20990,U.S.%20population%20%28844%20deaths%2F100%2C000%20people%29%20%5B2%5D%20More%20items</t>
+  </si>
+  <si>
+    <t>National Equity Atlas</t>
+  </si>
+  <si>
+    <t>https://nationalequityatlas.org/</t>
+  </si>
+  <si>
+    <t>National Household Travel Survey</t>
+  </si>
+  <si>
+    <t>https://nhts.ornl.gov/</t>
+  </si>
+  <si>
+    <t>National Land Cover Database (NLCD)</t>
+  </si>
+  <si>
+    <t>https://www.usgs.gov/centers/eros/science/national-land-cover-database</t>
+  </si>
+  <si>
+    <t>National Rivers Inventory</t>
+  </si>
+  <si>
+    <t>https://www.nps.gov/subjects/rivers/nationwide-rivers-inventory.htm</t>
+  </si>
+  <si>
+    <t>National Water and Recreation Trails Map</t>
+  </si>
+  <si>
+    <t>https://www.nrtapplication.org/trails</t>
+  </si>
+  <si>
+    <t>Nonprofit Spending Research Guide</t>
+  </si>
+  <si>
+    <t>https://guides.loc.gov/nonprofit-sector/form-990#:~:text=The%20990%20is%20a%20public,organization%20or%20from%20the%20IRS.</t>
+  </si>
+  <si>
+    <t>Library of Congress research guide on nonprofits</t>
+  </si>
+  <si>
+    <t>PAD-US Public Lands Map</t>
+  </si>
+  <si>
+    <t>https://www.usgs.gov/programs/gap-analysis-project/science/pad-us-data-overview</t>
+  </si>
+  <si>
+    <t>Racial Equity Data Lab</t>
+  </si>
+  <si>
+    <t>https://nationalequityatlas.org/lab#tools</t>
+  </si>
+  <si>
+    <t>Rails to Trails Conservancy</t>
+  </si>
+  <si>
+    <t>https://www.railstotrails.org/research/</t>
+  </si>
+  <si>
+    <t>Rail trail maps, research projects, BikeAble planner, etc.</t>
+  </si>
+  <si>
+    <t>TRAILS Decision Support Tool (USGS)</t>
+  </si>
+  <si>
+    <t>The Nature Conservancy Resilient Land Mapping Tool</t>
+  </si>
+  <si>
+    <t>https://www.maps.tnc.org/resilientland/</t>
+  </si>
+  <si>
+    <t>U.N. Tourism Data Dashboard</t>
+  </si>
+  <si>
+    <t>https://www.unwto.org/tourism-data/un-tourism-tourism-dashboard</t>
+  </si>
+  <si>
+    <t>Statistics and insights on key indicators for inbound and outbound tourism at global, regional, and national levels</t>
+  </si>
+  <si>
+    <t>USGS Trails Explorer</t>
+  </si>
+  <si>
+    <t>https://www.usgs.gov/tools/trails-explorer</t>
+  </si>
+  <si>
+    <t>Wilderness Connect – Wilderness Locator Map</t>
+  </si>
+  <si>
+    <t>https://arcg.is/1GCjnS</t>
+  </si>
+  <si>
+    <t>Work Zone Data Initiative</t>
+  </si>
+  <si>
+    <t>https://www.transportation.gov/av/data/wzdx</t>
+  </si>
+  <si>
+    <t>List of projects funded by AARP to make communities more livable for people of all ages</t>
+  </si>
+  <si>
+    <t>Analyzes transit quality through the social and economic impacts of transit</t>
+  </si>
+  <si>
+    <t>Maps shelters (with photos), vistas, and other assets along the Appalachian Trail</t>
+  </si>
+  <si>
+    <t>Super comprehensive collection of different mapping data from around the world</t>
+  </si>
+  <si>
+    <t>Search nonprofits to understand their funding</t>
+  </si>
+  <si>
+    <t>Sub-resource of National Equity Atlas that examines car access</t>
+  </si>
+  <si>
+    <t>Statistics</t>
+  </si>
+  <si>
+    <t>NPS Core Spacial Data Standard</t>
+  </si>
+  <si>
+    <t>Database and interactive map of all large-scale solar energy facilities in the U.S.</t>
+  </si>
+  <si>
+    <t>Equity, Statistics</t>
+  </si>
+  <si>
+    <t>Data that describe nationwide land cover and land change over nearly four decades</t>
+  </si>
+  <si>
+    <t>Filterable map of all water and recreation trails</t>
+  </si>
+  <si>
+    <t>Helps with creating visualizations; sub-resource of National Equity Atlas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The trail planning tool (TRAILS) is only available on request. Target users are those involved in the initial planning of new trails or improvements to existing trail routes or systems that would eventually be available in the public domain. Typically, participants work either directly for government land management agencies or partner with government land management agencies. </t>
+  </si>
+  <si>
+    <t>https://www.usgs.gov/tools/trails-trail-routing-analysis-and-information-linkage-system</t>
+  </si>
+  <si>
+    <t>For conservation planning with climate change in mind</t>
+  </si>
+  <si>
+    <t>Enables infrastructure owners and operators (IOOs) to make harmonized work zone data available for third party use.</t>
+  </si>
+  <si>
+    <t>Topic</t>
+  </si>
+  <si>
+    <t>Agency</t>
+  </si>
+  <si>
+    <t>Data Output</t>
+  </si>
+  <si>
+    <t>Livability, Age-Friendly, Equity</t>
+  </si>
+  <si>
+    <t>Maps</t>
+  </si>
+  <si>
+    <t>NPS</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Public Health</t>
+  </si>
+  <si>
+    <t>Climate Change</t>
+  </si>
+  <si>
+    <t>Trails</t>
+  </si>
+  <si>
+    <t>International</t>
+  </si>
+  <si>
+    <t>Maps, GIS</t>
+  </si>
+  <si>
+    <t>Nonprofits</t>
+  </si>
+  <si>
+    <t>Equity, Transportation</t>
+  </si>
+  <si>
+    <t>Tourism</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t>Tourism, International</t>
+  </si>
+  <si>
+    <t>USGS</t>
+  </si>
+  <si>
+    <t>Funding</t>
+  </si>
+  <si>
+    <t>Data Standards</t>
+  </si>
+  <si>
+    <t>FEMA</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>USDOT</t>
+  </si>
+  <si>
+    <t>United Nations</t>
+  </si>
+  <si>
+    <t>Data Standards, GIS</t>
+  </si>
+  <si>
+    <t>Maps, Statistics</t>
+  </si>
+  <si>
+    <t>Land</t>
+  </si>
+  <si>
+    <t>CDC</t>
+  </si>
+  <si>
+    <t>USFS</t>
+  </si>
+  <si>
+    <t>Government (other)</t>
+  </si>
+  <si>
+    <t>USFS, Nonprofits</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Trails, Appalachian Trail</t>
+  </si>
+  <si>
+    <t>Energy, Climate Change</t>
+  </si>
+  <si>
+    <t>Transportation, Travel</t>
+  </si>
+  <si>
     <t>Housing, Transportation, Equity</t>
   </si>
   <si>
-    <t>Large-Scale Solar Projects Map</t>
-  </si>
-  <si>
-    <t>https://www.usgs.gov/news/national-news-release/usgs-and-lawrence-berkeley-national-laboratory-release-database-and</t>
-  </si>
-  <si>
-    <t>NPS Mortality Data</t>
-  </si>
-  <si>
-    <t>https://www.nps.gov/orgs/1336/data.htm#:~:text=Key%20Mortality%20Statistics%3A%201%20A%20total%20of%20990,U.S.%20population%20%28844%20deaths%2F100%2C000%20people%29%20%5B2%5D%20More%20items</t>
-  </si>
-  <si>
-    <t>National Equity Atlas</t>
-  </si>
-  <si>
-    <t>https://nationalequityatlas.org/</t>
-  </si>
-  <si>
-    <t>National Household Travel Survey</t>
-  </si>
-  <si>
-    <t>https://nhts.ornl.gov/</t>
-  </si>
-  <si>
-    <t>National Land Cover Database (NLCD)</t>
-  </si>
-  <si>
-    <t>https://www.usgs.gov/centers/eros/science/national-land-cover-database</t>
-  </si>
-  <si>
-    <t>National Rivers Inventory</t>
-  </si>
-  <si>
-    <t>https://www.nps.gov/subjects/rivers/nationwide-rivers-inventory.htm</t>
-  </si>
-  <si>
-    <t>National Water and Recreation Trails Map</t>
-  </si>
-  <si>
-    <t>https://www.nrtapplication.org/trails</t>
-  </si>
-  <si>
-    <t>Nonprofit Spending Research Guide</t>
-  </si>
-  <si>
-    <t>https://guides.loc.gov/nonprofit-sector/form-990#:~:text=The%20990%20is%20a%20public,organization%20or%20from%20the%20IRS.</t>
-  </si>
-  <si>
-    <t>Library of Congress research guide on nonprofits</t>
-  </si>
-  <si>
-    <t>PAD-US Public Lands Map</t>
-  </si>
-  <si>
-    <t>https://www.usgs.gov/programs/gap-analysis-project/science/pad-us-data-overview</t>
-  </si>
-  <si>
-    <t>Racial Equity Data Lab</t>
-  </si>
-  <si>
-    <t>https://nationalequityatlas.org/lab#tools</t>
-  </si>
-  <si>
-    <t>Rails to Trails Conservancy</t>
-  </si>
-  <si>
-    <t>https://www.railstotrails.org/research/</t>
-  </si>
-  <si>
-    <t>Rail trail maps, research projects, BikeAble planner, etc.</t>
-  </si>
-  <si>
-    <t>TRAILS Decision Support Tool (USGS)</t>
-  </si>
-  <si>
-    <t>The Nature Conservancy Resilient Land Mapping Tool</t>
-  </si>
-  <si>
-    <t>https://www.maps.tnc.org/resilientland/</t>
-  </si>
-  <si>
-    <t>Maps, Climate Change, Conservation</t>
-  </si>
-  <si>
-    <t>U.N. Tourism Data Dashboard</t>
-  </si>
-  <si>
-    <t>https://www.unwto.org/tourism-data/un-tourism-tourism-dashboard</t>
-  </si>
-  <si>
-    <t>Statistics and insights on key indicators for inbound and outbound tourism at global, regional, and national levels</t>
-  </si>
-  <si>
-    <t>Tourism, International</t>
-  </si>
-  <si>
-    <t>USGS Trails Explorer</t>
-  </si>
-  <si>
-    <t>https://www.usgs.gov/tools/trails-explorer</t>
-  </si>
-  <si>
-    <t>Maps, Trails, USGS</t>
-  </si>
-  <si>
-    <t>Wilderness Connect – Wilderness Locator Map</t>
-  </si>
-  <si>
-    <t>https://arcg.is/1GCjnS</t>
-  </si>
-  <si>
-    <t>Work Zone Data Initiative</t>
-  </si>
-  <si>
-    <t>https://www.transportation.gov/av/data/wzdx</t>
-  </si>
-  <si>
-    <t>List of projects funded by AARP to make communities more livable for people of all ages</t>
-  </si>
-  <si>
-    <t>Analyzes transit quality through the social and economic impacts of transit</t>
-  </si>
-  <si>
-    <t>Maps shelters (with photos), vistas, and other assets along the Appalachian Trail</t>
-  </si>
-  <si>
-    <t>Maps, Trails, NPS, Appalachian Trail</t>
-  </si>
-  <si>
-    <t>Super comprehensive collection of different mapping data from around the world</t>
-  </si>
-  <si>
-    <t>Maps, GIS, International</t>
-  </si>
-  <si>
-    <t>Search nonprofits to understand their funding</t>
-  </si>
-  <si>
-    <t>Maps, Transportation</t>
-  </si>
-  <si>
-    <t>Sub-resource of National Equity Atlas that examines car access</t>
-  </si>
-  <si>
-    <t>Maps, Livability, Age-Friendly, Equity</t>
-  </si>
-  <si>
-    <t>Statistics</t>
-  </si>
-  <si>
-    <t>Equity, Transportation, Statistics</t>
-  </si>
-  <si>
-    <t>NPS Core Spacial Data Standard</t>
-  </si>
-  <si>
-    <t>Tourism, Statistics</t>
-  </si>
-  <si>
-    <t>Climate Change, FEMA</t>
-  </si>
-  <si>
-    <t>Maps, Public Health, CDC</t>
-  </si>
-  <si>
-    <t>Maps, Trails, USFS</t>
-  </si>
-  <si>
-    <t>Database and interactive map of all large-scale solar energy facilities in the U.S.</t>
-  </si>
-  <si>
-    <t>Maps, Energy, Climate Change, USGS</t>
-  </si>
-  <si>
-    <t>Equity, Statistics</t>
-  </si>
-  <si>
-    <t>NPS, Public Health</t>
-  </si>
-  <si>
-    <t>Transportation, Travel, Statistics</t>
-  </si>
-  <si>
-    <t>Data that describe nationwide land cover and land change over nearly four decades</t>
-  </si>
-  <si>
-    <t>USGS, Maps</t>
-  </si>
-  <si>
-    <t>NPS, Maps, Water</t>
-  </si>
-  <si>
-    <t>Filterable map of all water and recreation trails</t>
-  </si>
-  <si>
-    <t>Maps, Trails, Water</t>
-  </si>
-  <si>
-    <t>Maps, USGS</t>
-  </si>
-  <si>
-    <t>Helps with creating visualizations; sub-resource of National Equity Atlas</t>
-  </si>
-  <si>
-    <t>Maps, Trails, Biking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The trail planning tool (TRAILS) is only available on request. Target users are those involved in the initial planning of new trails or improvements to existing trail routes or systems that would eventually be available in the public domain. Typically, participants work either directly for government land management agencies or partner with government land management agencies. </t>
-  </si>
-  <si>
-    <t>https://www.usgs.gov/tools/trails-trail-routing-analysis-and-information-linkage-system</t>
-  </si>
-  <si>
-    <t>Trails, USGS</t>
-  </si>
-  <si>
-    <t>For conservation planning with climate change in mind</t>
-  </si>
-  <si>
-    <t>Maps, Wilderness</t>
-  </si>
-  <si>
-    <t>Enables infrastructure owners and operators (IOOs) to make harmonized work zone data available for third party use.</t>
+    <t>Trails, Water</t>
+  </si>
+  <si>
+    <t>Trails, Biking</t>
+  </si>
+  <si>
+    <t>Climate Change, Conservation</t>
+  </si>
+  <si>
+    <t>Wilderness, Trails</t>
   </si>
   <si>
     <t>Transportation, Infrastructure</t>
@@ -454,7 +499,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -464,6 +509,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -768,15 +819,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="3" width="50" customWidth="1"/>
     <col min="4" max="4" width="35" customWidth="1"/>
+    <col min="5" max="5" width="15" style="5" customWidth="1"/>
+    <col min="6" max="6" width="15.7265625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -787,425 +841,608 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="50" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="50" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="D10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="25" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="25" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E13" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="50" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="50" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="87.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="87.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="E29" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="25" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="37.5" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>117</v>
+        <v>132</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1217,6 +1454,8 @@
     <hyperlink ref="B20" r:id="rId5" xr:uid="{BBD5A0D8-64F4-4751-8253-2D297154C307}"/>
     <hyperlink ref="B25" r:id="rId6" location="tools" xr:uid="{7E999D70-B411-42FF-8C53-B6AF3A2DBB05}"/>
     <hyperlink ref="B27" r:id="rId7" xr:uid="{D4A02BE3-B4E9-49E3-B661-6228B78A50EC}"/>
+    <hyperlink ref="B15" r:id="rId8" xr:uid="{1FE3F742-C541-4274-A45E-D7FADAC9C2A9}"/>
+    <hyperlink ref="B32" r:id="rId9" xr:uid="{B641EC6D-3FAC-481F-9400-7F1B08500579}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
